--- a/Sample_Info.xlsx
+++ b/Sample_Info.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CAMILA MOREIRA\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11DFA7DD-E417-4616-8685-2B65932830B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11FE2409-91B2-4BF6-9ECD-2C17ACB455A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{918E8ED7-0FA4-4B48-B036-1030E53DFD57}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="485">
   <si>
     <t>PET_1</t>
   </si>
@@ -968,6 +968,534 @@
   </si>
   <si>
     <t>Roast Chicken Box Lid</t>
+  </si>
+  <si>
+    <t>PP_24</t>
+  </si>
+  <si>
+    <t>Tampa caixa cotonetes bebe</t>
+  </si>
+  <si>
+    <t>HDPE_61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detergente Roupa Botanical Origin </t>
+  </si>
+  <si>
+    <t>Brown</t>
+  </si>
+  <si>
+    <t>flat</t>
+  </si>
+  <si>
+    <t>PET_47</t>
+  </si>
+  <si>
+    <t>Soro Fisiologico 500 mL Wells</t>
+  </si>
+  <si>
+    <t>curved</t>
+  </si>
+  <si>
+    <t>PET_48</t>
+  </si>
+  <si>
+    <t>OGX Bond Protein Repair</t>
+  </si>
+  <si>
+    <t>No color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1mm </t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>28 mm*45.7 mm</t>
+  </si>
+  <si>
+    <t>25 mm *37 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5 mm * 13.8 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">r= 49 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 mm * 32.7 mm </t>
+  </si>
+  <si>
+    <t>27.2 mm * 42.6 mm</t>
+  </si>
+  <si>
+    <t>20 mm * 43.5 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 mm * 37.2 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 mm * 20 mm </t>
+  </si>
+  <si>
+    <t>27.8 mm * 24.3 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3 mm *23.5 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4 mm * 32.2 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7 mm * 50 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1 mm * 35.4 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7 mm * 32.9 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8 mm * 39.8 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">42 mm * 38 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6 mm * 25.6 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4 mm * 48 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 mm * 38 mm </t>
+  </si>
+  <si>
+    <t>16 mm * 20 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5 mm 31.5 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2 mm 54.9 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8 mm 49 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 mm * 28 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 mm * 52.6 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6 mm * 32.4 mm </t>
+  </si>
+  <si>
+    <t>31.8 mm * 41 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 mm * 38.7 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 mm * 29.5 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6 mm * 24.5 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9 mm * 44.4 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5 mm * 37.9 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 mm * 37.2 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 mm * 16 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3 mm * 50.6 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7 mm * 49.3 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2 mm * 21.7 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2 mm * 29 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8 mm * 30.7 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7 mm * 35.8 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4 mm * 30 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 mm * 39 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4 mm *27 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3 mm * 46.9 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 mm *42.2 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7 mm * 29 mm </t>
+  </si>
+  <si>
+    <t>r= 45.7 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8 mm * 37 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5 mm * 30.2 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6 mm * 35.9 mm </t>
+  </si>
+  <si>
+    <t>25.4 mm * 30.5 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4 mm * 21.1 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4 mm * 33 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7 mm * 35.4 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6 mm * 45.1 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4 mm * 27.4 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3 mm * 30.0 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5 mm * 27.4 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 mm * 16.9 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8 mm * 36.5 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5 mm * 28 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6 mm * 31.1 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2 mm * 38 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2 mm * 20.0 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4 mm * 25.9 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4 mm * 46.8 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4 mm * 28 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4 mm * 50.6 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2 mm * 42.4 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7 mm * 31.7 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">r=38.2 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1 mm * 37 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8 mm * 42.2 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2 mm *  37.6 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 mm * 23.8 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8 mm * 22.3 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2 mm * 30.0 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8 mm * 37 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1 mm * 39.8 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6 mm * 69.7 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6 mm * 62.7 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3 mm * 59.3 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5 mm * 23.2 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6 mm * 27.5 mm </t>
+  </si>
+  <si>
+    <t>28.6 mm * 41.2 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4 mm * 41.5 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6 mm * 42.6 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2 mm * 41 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2 mm * 34.7 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2 mm * 34.4 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3 mm *44.5 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6 mm * 19.1 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1 mm *42.3 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4 mm * 38.3 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2 mm * 33.4 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8 mm * 40.4 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5 mm * 29.5 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8 mm * 36.2 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4 mm * 25.8 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4 mm * 26.4 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1 mm * 38.4 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4 mm * 25.4 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4 mm * 31.7 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8 mm * 29.1 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8 mm * 22.7 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6 mm * 36.1 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5 mm * 29.3 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5 mm * 37.6 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2 mm * 27.5 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.3 mm * 37 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6 mm *32.9 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3 mm * 32.9 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6 mm * 27.8 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 mm * 41.7 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6 mm * 33.8 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9 mm * 35 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8 mm * 42.9 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7  mm * 35.8 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8 mm * 40.4 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7 mm * 31.5 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7 mm * 38.5 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 mm * 30.6 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7 mm * 34.5 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5 mm * 46.7 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8 mm * 39.6 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 mm * 36.5 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7 mm * 21.7 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2 mm * 27.6 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1 mm * 34.4 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1 mm * 40 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 mm * 21.8 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8 mm * 24.5 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1 mm * 30.3 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4 mm * 32 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4 mm * 35.6 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1 mm * 27.8 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8 mm * 26.6 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1 mm * 39.5 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2 mm * 37.4 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3 mm * 38.7 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8 mm * 30.9 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5 mm * 48.5 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9 mm * 34.4 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6 mm * 39.6 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5 mm * 28.5 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6 mm * 65.4 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9 mm * 47.8 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">r=15.3 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7 mm * 49.3 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9 mm * 34.6 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5 mm * 44.5 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 mm * 15 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9 mm * 38.5 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8 mm * 41 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9 mm * 38.1 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4 mm </t>
   </si>
 </sst>
 </file>
@@ -1059,7 +1587,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1077,8 +1605,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1413,21 +1939,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37B73843-F9F8-40BF-BD87-31FC1536CE03}">
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="42.88671875" customWidth="1"/>
     <col min="3" max="3" width="19.5546875" customWidth="1"/>
     <col min="4" max="5" width="16.21875" customWidth="1"/>
-    <col min="6" max="6" width="15.21875" customWidth="1"/>
-    <col min="7" max="7" width="17.5546875" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" customWidth="1"/>
-    <col min="10" max="10" width="18.77734375" style="9" customWidth="1"/>
-    <col min="11" max="11" width="8.88671875" style="9"/>
+    <col min="6" max="6" width="20.21875" customWidth="1"/>
+    <col min="7" max="7" width="15.21875" customWidth="1"/>
+    <col min="8" max="8" width="17.5546875" customWidth="1"/>
+    <col min="9" max="9" width="15.5546875" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" customWidth="1"/>
+    <col min="11" max="11" width="18.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>35</v>
       </c>
@@ -1443,22 +1969,23 @@
       <c r="E1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="J1"/>
-      <c r="K1"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -1475,21 +2002,22 @@
         <v>45</v>
       </c>
       <c r="F2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G2" t="s">
         <v>51</v>
       </c>
-      <c r="G2" t="s">
-        <v>22</v>
-      </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J2"/>
-      <c r="K2"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1506,21 +2034,22 @@
         <v>44</v>
       </c>
       <c r="F3" t="s">
+        <v>354</v>
+      </c>
+      <c r="G3" t="s">
         <v>51</v>
       </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>46</v>
-      </c>
-      <c r="J3"/>
-      <c r="K3"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -1537,21 +2066,22 @@
         <v>44</v>
       </c>
       <c r="F4" t="s">
+        <v>478</v>
+      </c>
+      <c r="G4" t="s">
         <v>51</v>
       </c>
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4"/>
-      <c r="K4"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
@@ -1568,21 +2098,22 @@
         <v>45</v>
       </c>
       <c r="F5" t="s">
+        <v>377</v>
+      </c>
+      <c r="G5" t="s">
         <v>51</v>
       </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5"/>
-      <c r="K5"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
@@ -1599,21 +2130,22 @@
         <v>45</v>
       </c>
       <c r="F6" t="s">
+        <v>328</v>
+      </c>
+      <c r="G6" t="s">
         <v>52</v>
       </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I6" t="s">
-        <v>46</v>
-      </c>
-      <c r="J6"/>
-      <c r="K6"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
@@ -1630,21 +2162,22 @@
         <v>45</v>
       </c>
       <c r="F7" t="s">
+        <v>347</v>
+      </c>
+      <c r="G7" t="s">
         <v>50</v>
       </c>
-      <c r="G7" t="s">
-        <v>22</v>
-      </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I7" t="s">
-        <v>46</v>
-      </c>
-      <c r="J7"/>
-      <c r="K7"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
@@ -1661,21 +2194,22 @@
         <v>45</v>
       </c>
       <c r="F8" t="s">
+        <v>356</v>
+      </c>
+      <c r="G8" t="s">
         <v>50</v>
       </c>
-      <c r="G8" t="s">
-        <v>22</v>
-      </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I8" t="s">
-        <v>46</v>
-      </c>
-      <c r="J8"/>
-      <c r="K8"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>54</v>
       </c>
@@ -1692,21 +2226,22 @@
         <v>45</v>
       </c>
       <c r="F9" t="s">
+        <v>334</v>
+      </c>
+      <c r="G9" t="s">
         <v>56</v>
       </c>
-      <c r="G9" t="s">
-        <v>22</v>
-      </c>
       <c r="H9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I9" t="s">
-        <v>46</v>
-      </c>
-      <c r="J9"/>
-      <c r="K9"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>59</v>
       </c>
@@ -1723,21 +2258,22 @@
         <v>44</v>
       </c>
       <c r="F10" t="s">
+        <v>471</v>
+      </c>
+      <c r="G10" t="s">
         <v>64</v>
       </c>
-      <c r="G10" t="s">
-        <v>22</v>
-      </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>46</v>
-      </c>
-      <c r="J10"/>
-      <c r="K10"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>61</v>
       </c>
@@ -1754,21 +2290,22 @@
         <v>44</v>
       </c>
       <c r="F11" t="s">
+        <v>470</v>
+      </c>
+      <c r="G11" t="s">
         <v>66</v>
       </c>
-      <c r="G11" t="s">
-        <v>22</v>
-      </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I11" t="s">
-        <v>46</v>
-      </c>
-      <c r="J11"/>
-      <c r="K11"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>70</v>
       </c>
@@ -1785,21 +2322,22 @@
         <v>45</v>
       </c>
       <c r="F12" t="s">
+        <v>327</v>
+      </c>
+      <c r="G12" t="s">
         <v>210</v>
       </c>
-      <c r="G12" t="s">
-        <v>22</v>
-      </c>
       <c r="H12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I12" t="s">
-        <v>46</v>
-      </c>
-      <c r="J12"/>
-      <c r="K12"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>72</v>
       </c>
@@ -1816,21 +2354,22 @@
         <v>44</v>
       </c>
       <c r="F13" t="s">
+        <v>339</v>
+      </c>
+      <c r="G13" t="s">
         <v>81</v>
       </c>
-      <c r="G13" t="s">
-        <v>22</v>
-      </c>
       <c r="H13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I13" t="s">
-        <v>46</v>
-      </c>
-      <c r="J13"/>
-      <c r="K13"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>75</v>
       </c>
@@ -1847,21 +2386,22 @@
         <v>44</v>
       </c>
       <c r="F14" t="s">
+        <v>324</v>
+      </c>
+      <c r="G14" t="s">
         <v>56</v>
       </c>
-      <c r="G14" t="s">
-        <v>22</v>
-      </c>
       <c r="H14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I14" t="s">
-        <v>46</v>
-      </c>
-      <c r="J14"/>
-      <c r="K14"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>76</v>
       </c>
@@ -1878,21 +2418,22 @@
         <v>44</v>
       </c>
       <c r="F15" t="s">
+        <v>349</v>
+      </c>
+      <c r="G15" t="s">
         <v>81</v>
       </c>
-      <c r="G15" t="s">
-        <v>22</v>
-      </c>
       <c r="H15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I15" t="s">
-        <v>46</v>
-      </c>
-      <c r="J15"/>
-      <c r="K15"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>92</v>
       </c>
@@ -1909,19 +2450,20 @@
         <v>44</v>
       </c>
       <c r="F16" t="s">
+        <v>355</v>
+      </c>
+      <c r="G16" t="s">
         <v>81</v>
       </c>
-      <c r="G16" t="s">
-        <v>22</v>
-      </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I16" t="s">
-        <v>46</v>
-      </c>
-      <c r="J16"/>
-      <c r="K16"/>
+        <v>21</v>
+      </c>
+      <c r="J16" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
@@ -1940,19 +2482,20 @@
         <v>44</v>
       </c>
       <c r="F17" t="s">
+        <v>336</v>
+      </c>
+      <c r="G17" t="s">
         <v>56</v>
       </c>
-      <c r="G17" t="s">
-        <v>22</v>
-      </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I17" t="s">
-        <v>46</v>
-      </c>
-      <c r="J17"/>
-      <c r="K17"/>
+        <v>21</v>
+      </c>
+      <c r="J17" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
@@ -1971,19 +2514,20 @@
         <v>44</v>
       </c>
       <c r="F18" t="s">
+        <v>340</v>
+      </c>
+      <c r="G18" t="s">
         <v>81</v>
       </c>
-      <c r="G18" t="s">
-        <v>22</v>
-      </c>
       <c r="H18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I18" t="s">
-        <v>46</v>
-      </c>
-      <c r="J18"/>
-      <c r="K18"/>
+        <v>21</v>
+      </c>
+      <c r="J18" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
@@ -2002,19 +2546,20 @@
         <v>44</v>
       </c>
       <c r="F19" t="s">
+        <v>420</v>
+      </c>
+      <c r="G19" t="s">
         <v>209</v>
       </c>
-      <c r="G19" t="s">
-        <v>22</v>
-      </c>
       <c r="H19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I19" t="s">
-        <v>46</v>
-      </c>
-      <c r="J19"/>
-      <c r="K19"/>
+        <v>21</v>
+      </c>
+      <c r="J19" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
@@ -2033,15 +2578,18 @@
         <v>44</v>
       </c>
       <c r="F20" t="s">
+        <v>329</v>
+      </c>
+      <c r="G20" t="s">
         <v>81</v>
       </c>
-      <c r="G20" t="s">
-        <v>22</v>
-      </c>
       <c r="H20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I20" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2062,15 +2610,18 @@
         <v>44</v>
       </c>
       <c r="F21" t="s">
+        <v>357</v>
+      </c>
+      <c r="G21" t="s">
         <v>81</v>
       </c>
-      <c r="G21" t="s">
-        <v>22</v>
-      </c>
       <c r="H21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I21" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2091,18 +2642,21 @@
         <v>44</v>
       </c>
       <c r="F22" t="s">
+        <v>331</v>
+      </c>
+      <c r="G22" t="s">
         <v>81</v>
       </c>
-      <c r="G22" t="s">
-        <v>22</v>
-      </c>
       <c r="H22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I22" t="s">
-        <v>46</v>
-      </c>
-      <c r="J22" s="10"/>
+        <v>21</v>
+      </c>
+      <c r="J22" t="s">
+        <v>46</v>
+      </c>
+      <c r="K22" s="6"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
@@ -2121,15 +2675,18 @@
         <v>44</v>
       </c>
       <c r="F23" t="s">
+        <v>342</v>
+      </c>
+      <c r="G23" t="s">
         <v>81</v>
       </c>
-      <c r="G23" t="s">
-        <v>22</v>
-      </c>
       <c r="H23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I23" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2150,15 +2707,18 @@
         <v>44</v>
       </c>
       <c r="F24" t="s">
+        <v>448</v>
+      </c>
+      <c r="G24" t="s">
         <v>56</v>
       </c>
-      <c r="G24" t="s">
-        <v>22</v>
-      </c>
       <c r="H24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2179,15 +2739,18 @@
         <v>44</v>
       </c>
       <c r="F25" t="s">
+        <v>364</v>
+      </c>
+      <c r="G25" t="s">
         <v>81</v>
       </c>
-      <c r="G25" t="s">
-        <v>22</v>
-      </c>
       <c r="H25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I25" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2208,15 +2771,18 @@
         <v>44</v>
       </c>
       <c r="F26" t="s">
+        <v>383</v>
+      </c>
+      <c r="G26" t="s">
         <v>64</v>
       </c>
-      <c r="G26" t="s">
-        <v>22</v>
-      </c>
       <c r="H26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2237,15 +2803,18 @@
         <v>44</v>
       </c>
       <c r="F27" t="s">
+        <v>451</v>
+      </c>
+      <c r="G27" t="s">
         <v>81</v>
       </c>
-      <c r="G27" t="s">
-        <v>22</v>
-      </c>
       <c r="H27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I27" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2266,15 +2835,18 @@
         <v>44</v>
       </c>
       <c r="F28" t="s">
+        <v>423</v>
+      </c>
+      <c r="G28" t="s">
         <v>64</v>
       </c>
-      <c r="G28" t="s">
-        <v>22</v>
-      </c>
       <c r="H28" t="s">
         <v>22</v>
       </c>
       <c r="I28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2295,15 +2867,18 @@
         <v>44</v>
       </c>
       <c r="F29" t="s">
+        <v>422</v>
+      </c>
+      <c r="G29" t="s">
         <v>56</v>
       </c>
-      <c r="G29" t="s">
-        <v>22</v>
-      </c>
       <c r="H29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I29" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2324,15 +2899,18 @@
         <v>44</v>
       </c>
       <c r="F30" t="s">
+        <v>397</v>
+      </c>
+      <c r="G30" t="s">
         <v>56</v>
       </c>
-      <c r="G30" t="s">
-        <v>22</v>
-      </c>
       <c r="H30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I30" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2353,15 +2931,18 @@
         <v>44</v>
       </c>
       <c r="F31" t="s">
+        <v>436</v>
+      </c>
+      <c r="G31" t="s">
         <v>56</v>
       </c>
-      <c r="G31" t="s">
-        <v>22</v>
-      </c>
       <c r="H31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I31" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2382,20 +2963,23 @@
         <v>44</v>
       </c>
       <c r="F32" t="s">
+        <v>373</v>
+      </c>
+      <c r="G32" t="s">
         <v>81</v>
       </c>
-      <c r="G32" t="s">
-        <v>22</v>
-      </c>
       <c r="H32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I32" t="s">
-        <v>46</v>
-      </c>
-      <c r="J32" s="10"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J32" t="s">
+        <v>46</v>
+      </c>
+      <c r="K32" s="6"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>148</v>
       </c>
@@ -2412,20 +2996,23 @@
         <v>44</v>
       </c>
       <c r="F33" t="s">
+        <v>370</v>
+      </c>
+      <c r="G33" t="s">
         <v>56</v>
       </c>
-      <c r="G33" t="s">
-        <v>22</v>
-      </c>
       <c r="H33" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" t="s">
-        <v>46</v>
-      </c>
-      <c r="J33" s="10"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J33" t="s">
+        <v>46</v>
+      </c>
+      <c r="K33" s="6"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>149</v>
       </c>
@@ -2442,19 +3029,22 @@
         <v>44</v>
       </c>
       <c r="F34" t="s">
+        <v>455</v>
+      </c>
+      <c r="G34" t="s">
         <v>209</v>
       </c>
-      <c r="G34" t="s">
-        <v>22</v>
-      </c>
       <c r="H34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I34" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J34" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>166</v>
       </c>
@@ -2471,19 +3061,22 @@
         <v>44</v>
       </c>
       <c r="F35" t="s">
+        <v>449</v>
+      </c>
+      <c r="G35" t="s">
         <v>56</v>
       </c>
-      <c r="G35" t="s">
-        <v>22</v>
-      </c>
       <c r="H35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I35" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J35" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>168</v>
       </c>
@@ -2500,19 +3093,22 @@
         <v>44</v>
       </c>
       <c r="F36" t="s">
+        <v>457</v>
+      </c>
+      <c r="G36" t="s">
         <v>56</v>
       </c>
-      <c r="G36" t="s">
-        <v>22</v>
-      </c>
       <c r="H36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I36" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>169</v>
       </c>
@@ -2529,20 +3125,23 @@
         <v>44</v>
       </c>
       <c r="F37" t="s">
+        <v>365</v>
+      </c>
+      <c r="G37" t="s">
         <v>56</v>
       </c>
-      <c r="G37" t="s">
-        <v>22</v>
-      </c>
       <c r="H37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I37" t="s">
-        <v>46</v>
-      </c>
-      <c r="J37" s="10"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s">
+        <v>46</v>
+      </c>
+      <c r="K37" s="6"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>179</v>
       </c>
@@ -2559,19 +3158,22 @@
         <v>44</v>
       </c>
       <c r="F38" t="s">
+        <v>445</v>
+      </c>
+      <c r="G38" t="s">
         <v>56</v>
       </c>
-      <c r="G38" t="s">
-        <v>22</v>
-      </c>
       <c r="H38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I38" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J38" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>180</v>
       </c>
@@ -2588,20 +3190,23 @@
         <v>44</v>
       </c>
       <c r="F39" t="s">
+        <v>371</v>
+      </c>
+      <c r="G39" t="s">
         <v>56</v>
       </c>
-      <c r="G39" t="s">
-        <v>22</v>
-      </c>
       <c r="H39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I39" t="s">
-        <v>46</v>
-      </c>
-      <c r="J39" s="10"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J39" t="s">
+        <v>46</v>
+      </c>
+      <c r="K39" s="6"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>181</v>
       </c>
@@ -2618,20 +3223,23 @@
         <v>44</v>
       </c>
       <c r="F40" t="s">
+        <v>387</v>
+      </c>
+      <c r="G40" t="s">
         <v>209</v>
       </c>
-      <c r="G40" t="s">
-        <v>22</v>
-      </c>
       <c r="H40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I40" t="s">
-        <v>46</v>
-      </c>
-      <c r="J40" s="10"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J40" t="s">
+        <v>46</v>
+      </c>
+      <c r="K40" s="6"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>186</v>
       </c>
@@ -2648,20 +3256,23 @@
         <v>44</v>
       </c>
       <c r="F41" t="s">
+        <v>374</v>
+      </c>
+      <c r="G41" t="s">
         <v>56</v>
       </c>
-      <c r="G41" t="s">
-        <v>22</v>
-      </c>
       <c r="H41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I41" t="s">
-        <v>46</v>
-      </c>
-      <c r="J41" s="10"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s">
+        <v>46</v>
+      </c>
+      <c r="K41" s="6"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>187</v>
       </c>
@@ -2678,19 +3289,22 @@
         <v>44</v>
       </c>
       <c r="F42" t="s">
+        <v>458</v>
+      </c>
+      <c r="G42" t="s">
         <v>56</v>
       </c>
-      <c r="G42" t="s">
-        <v>22</v>
-      </c>
       <c r="H42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I42" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>189</v>
       </c>
@@ -2707,19 +3321,22 @@
         <v>44</v>
       </c>
       <c r="F43" t="s">
+        <v>438</v>
+      </c>
+      <c r="G43" t="s">
         <v>56</v>
       </c>
-      <c r="G43" t="s">
-        <v>22</v>
-      </c>
       <c r="H43" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I43" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J43" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>217</v>
       </c>
@@ -2735,17 +3352,23 @@
       <c r="E44" t="s">
         <v>45</v>
       </c>
+      <c r="F44" t="s">
+        <v>437</v>
+      </c>
       <c r="G44" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="H44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I44" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J44" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>218</v>
       </c>
@@ -2761,17 +3384,23 @@
       <c r="E45" t="s">
         <v>44</v>
       </c>
+      <c r="F45" t="s">
+        <v>452</v>
+      </c>
       <c r="G45" t="s">
-        <v>22</v>
+        <v>477</v>
       </c>
       <c r="H45" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I45" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J45" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>219</v>
       </c>
@@ -2787,17 +3416,23 @@
       <c r="E46" t="s">
         <v>45</v>
       </c>
+      <c r="F46" t="s">
+        <v>406</v>
+      </c>
       <c r="G46" t="s">
-        <v>22</v>
+        <v>476</v>
       </c>
       <c r="H46" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I46" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>221</v>
       </c>
@@ -2813,14 +3448,66 @@
       <c r="E47" t="s">
         <v>44</v>
       </c>
+      <c r="F47" t="s">
+        <v>375</v>
+      </c>
       <c r="G47" t="s">
-        <v>22</v>
+        <v>484</v>
       </c>
       <c r="H47" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I47" t="s">
-        <v>46</v>
+        <v>21</v>
+      </c>
+      <c r="J47" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B48" t="s">
+        <v>316</v>
+      </c>
+      <c r="C48" t="s">
+        <v>248</v>
+      </c>
+      <c r="D48" t="s">
+        <v>90</v>
+      </c>
+      <c r="E48" t="s">
+        <v>317</v>
+      </c>
+      <c r="F48" t="s">
+        <v>468</v>
+      </c>
+      <c r="G48" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B49" t="s">
+        <v>319</v>
+      </c>
+      <c r="C49" t="s">
+        <v>320</v>
+      </c>
+      <c r="D49" t="s">
+        <v>89</v>
+      </c>
+      <c r="E49" t="s">
+        <v>45</v>
+      </c>
+      <c r="F49" t="s">
+        <v>467</v>
+      </c>
+      <c r="G49" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -2831,22 +3518,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59AE9756-20F4-459C-8F4E-A56EBC95A915}">
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="40.6640625" customWidth="1"/>
     <col min="3" max="3" width="8.88671875" customWidth="1"/>
     <col min="4" max="4" width="16.33203125" customWidth="1"/>
     <col min="5" max="5" width="15.21875" customWidth="1"/>
-    <col min="6" max="6" width="22.21875" customWidth="1"/>
-    <col min="7" max="7" width="19.21875" customWidth="1"/>
-    <col min="8" max="8" width="17.77734375" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="16.109375" customWidth="1"/>
+    <col min="6" max="6" width="17.88671875" customWidth="1"/>
+    <col min="7" max="7" width="22.21875" customWidth="1"/>
+    <col min="8" max="8" width="19.21875" customWidth="1"/>
+    <col min="9" max="9" width="17.77734375" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>35</v>
       </c>
@@ -2862,20 +3550,21 @@
       <c r="E1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3"/>
+      <c r="G1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
@@ -2892,19 +3581,22 @@
         <v>276</v>
       </c>
       <c r="F2" t="s">
+        <v>346</v>
+      </c>
+      <c r="G2" t="s">
         <v>47</v>
       </c>
-      <c r="G2" t="s">
-        <v>22</v>
-      </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
@@ -2921,19 +3613,22 @@
         <v>44</v>
       </c>
       <c r="F3" t="s">
+        <v>350</v>
+      </c>
+      <c r="G3" t="s">
         <v>47</v>
       </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
@@ -2949,17 +3644,23 @@
       <c r="E4" t="s">
         <v>44</v>
       </c>
+      <c r="F4" t="s">
+        <v>344</v>
+      </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>476</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>12</v>
       </c>
@@ -2976,19 +3677,22 @@
         <v>45</v>
       </c>
       <c r="F5" t="s">
+        <v>392</v>
+      </c>
+      <c r="G5" t="s">
         <v>48</v>
       </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>13</v>
       </c>
@@ -3005,19 +3709,22 @@
         <v>44</v>
       </c>
       <c r="F6" t="s">
+        <v>337</v>
+      </c>
+      <c r="G6" t="s">
         <v>53</v>
       </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
       <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
         <v>28</v>
       </c>
-      <c r="I6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
@@ -3034,19 +3741,22 @@
         <v>44</v>
       </c>
       <c r="F7" t="s">
+        <v>351</v>
+      </c>
+      <c r="G7" t="s">
         <v>47</v>
       </c>
-      <c r="G7" t="s">
-        <v>22</v>
-      </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>15</v>
       </c>
@@ -3062,17 +3772,23 @@
       <c r="E8" t="s">
         <v>44</v>
       </c>
+      <c r="F8" t="s">
+        <v>376</v>
+      </c>
       <c r="G8" t="s">
-        <v>22</v>
+        <v>321</v>
       </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>16</v>
       </c>
@@ -3088,17 +3804,23 @@
       <c r="E9" t="s">
         <v>44</v>
       </c>
+      <c r="F9" t="s">
+        <v>358</v>
+      </c>
       <c r="G9" t="s">
-        <v>22</v>
+        <v>477</v>
       </c>
       <c r="H9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>17</v>
       </c>
@@ -3114,17 +3836,23 @@
       <c r="E10" t="s">
         <v>44</v>
       </c>
+      <c r="F10" t="s">
+        <v>361</v>
+      </c>
       <c r="G10" t="s">
-        <v>22</v>
+        <v>480</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>18</v>
       </c>
@@ -3140,17 +3868,23 @@
       <c r="E11" t="s">
         <v>44</v>
       </c>
+      <c r="F11" t="s">
+        <v>326</v>
+      </c>
       <c r="G11" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>57</v>
       </c>
@@ -3167,19 +3901,22 @@
         <v>44</v>
       </c>
       <c r="F12" t="s">
+        <v>405</v>
+      </c>
+      <c r="G12" t="s">
         <v>66</v>
       </c>
-      <c r="G12" t="s">
-        <v>22</v>
-      </c>
       <c r="H12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>60</v>
       </c>
@@ -3196,19 +3933,22 @@
         <v>44</v>
       </c>
       <c r="F13" t="s">
+        <v>475</v>
+      </c>
+      <c r="G13" t="s">
         <v>64</v>
       </c>
-      <c r="G13" t="s">
-        <v>22</v>
-      </c>
       <c r="H13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>73</v>
       </c>
@@ -3225,19 +3965,22 @@
         <v>44</v>
       </c>
       <c r="F14" t="s">
+        <v>338</v>
+      </c>
+      <c r="G14" t="s">
         <v>80</v>
       </c>
-      <c r="G14" t="s">
-        <v>22</v>
-      </c>
       <c r="H14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I14" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>74</v>
       </c>
@@ -3254,19 +3997,22 @@
         <v>44</v>
       </c>
       <c r="F15" t="s">
+        <v>348</v>
+      </c>
+      <c r="G15" t="s">
         <v>80</v>
       </c>
-      <c r="G15" t="s">
-        <v>22</v>
-      </c>
       <c r="H15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>104</v>
       </c>
@@ -3283,19 +4029,22 @@
         <v>45</v>
       </c>
       <c r="F16" t="s">
+        <v>333</v>
+      </c>
+      <c r="G16" t="s">
         <v>80</v>
       </c>
-      <c r="G16" t="s">
-        <v>22</v>
-      </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>106</v>
       </c>
@@ -3312,19 +4061,22 @@
         <v>44</v>
       </c>
       <c r="F17" t="s">
+        <v>335</v>
+      </c>
+      <c r="G17" t="s">
         <v>64</v>
       </c>
-      <c r="G17" t="s">
-        <v>22</v>
-      </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>109</v>
       </c>
@@ -3341,19 +4093,22 @@
         <v>45</v>
       </c>
       <c r="F18" t="s">
+        <v>384</v>
+      </c>
+      <c r="G18" t="s">
         <v>80</v>
       </c>
-      <c r="G18" t="s">
-        <v>22</v>
-      </c>
       <c r="H18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>116</v>
       </c>
@@ -3370,19 +4125,22 @@
         <v>45</v>
       </c>
       <c r="F19" t="s">
+        <v>391</v>
+      </c>
+      <c r="G19" t="s">
         <v>210</v>
       </c>
-      <c r="G19" t="s">
-        <v>22</v>
-      </c>
       <c r="H19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>118</v>
       </c>
@@ -3399,19 +4157,22 @@
         <v>45</v>
       </c>
       <c r="F20" t="s">
+        <v>394</v>
+      </c>
+      <c r="G20" t="s">
         <v>210</v>
       </c>
-      <c r="G20" t="s">
-        <v>22</v>
-      </c>
       <c r="H20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>119</v>
       </c>
@@ -3428,19 +4189,22 @@
         <v>44</v>
       </c>
       <c r="F21" t="s">
+        <v>456</v>
+      </c>
+      <c r="G21" t="s">
         <v>85</v>
       </c>
-      <c r="G21" t="s">
-        <v>22</v>
-      </c>
       <c r="H21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>120</v>
       </c>
@@ -3457,20 +4221,23 @@
         <v>44</v>
       </c>
       <c r="F22" t="s">
+        <v>479</v>
+      </c>
+      <c r="G22" t="s">
         <v>210</v>
       </c>
-      <c r="G22" t="s">
-        <v>22</v>
-      </c>
       <c r="H22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I22" t="s">
-        <v>46</v>
-      </c>
-      <c r="K22" s="6"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s">
+        <v>46</v>
+      </c>
+      <c r="L22" s="6"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>122</v>
       </c>
@@ -3487,19 +4254,22 @@
         <v>45</v>
       </c>
       <c r="F23" t="s">
+        <v>398</v>
+      </c>
+      <c r="G23" t="s">
         <v>210</v>
       </c>
-      <c r="G23" t="s">
-        <v>22</v>
-      </c>
       <c r="H23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I23" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>123</v>
       </c>
@@ -3516,19 +4286,22 @@
         <v>45</v>
       </c>
       <c r="F24" t="s">
+        <v>401</v>
+      </c>
+      <c r="G24" t="s">
         <v>210</v>
       </c>
-      <c r="G24" t="s">
-        <v>22</v>
-      </c>
       <c r="H24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I24" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>124</v>
       </c>
@@ -3545,19 +4318,22 @@
         <v>45</v>
       </c>
       <c r="F25" t="s">
+        <v>417</v>
+      </c>
+      <c r="G25" t="s">
         <v>210</v>
       </c>
-      <c r="G25" t="s">
-        <v>22</v>
-      </c>
       <c r="H25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I25" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>125</v>
       </c>
@@ -3574,19 +4350,22 @@
         <v>45</v>
       </c>
       <c r="F26" t="s">
+        <v>432</v>
+      </c>
+      <c r="G26" t="s">
         <v>210</v>
       </c>
-      <c r="G26" t="s">
-        <v>22</v>
-      </c>
       <c r="H26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I26" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>128</v>
       </c>
@@ -3603,20 +4382,23 @@
         <v>44</v>
       </c>
       <c r="F27" t="s">
+        <v>389</v>
+      </c>
+      <c r="G27" t="s">
         <v>65</v>
       </c>
-      <c r="G27" t="s">
-        <v>22</v>
-      </c>
       <c r="H27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I27" t="s">
-        <v>46</v>
-      </c>
-      <c r="K27" s="6"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J27" t="s">
+        <v>46</v>
+      </c>
+      <c r="L27" s="6"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>133</v>
       </c>
@@ -3633,19 +4415,22 @@
         <v>44</v>
       </c>
       <c r="F28" t="s">
+        <v>388</v>
+      </c>
+      <c r="G28" t="s">
         <v>84</v>
       </c>
-      <c r="G28" t="s">
-        <v>22</v>
-      </c>
       <c r="H28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I28" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J28" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>135</v>
       </c>
@@ -3662,20 +4447,23 @@
         <v>45</v>
       </c>
       <c r="F29" t="s">
+        <v>382</v>
+      </c>
+      <c r="G29" t="s">
         <v>85</v>
       </c>
-      <c r="G29" t="s">
-        <v>22</v>
-      </c>
       <c r="H29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I29" t="s">
-        <v>46</v>
-      </c>
-      <c r="K29" s="6"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J29" t="s">
+        <v>46</v>
+      </c>
+      <c r="L29" s="6"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>138</v>
       </c>
@@ -3692,20 +4480,23 @@
         <v>44</v>
       </c>
       <c r="F30" t="s">
+        <v>362</v>
+      </c>
+      <c r="G30" t="s">
         <v>85</v>
       </c>
-      <c r="G30" t="s">
-        <v>22</v>
-      </c>
       <c r="H30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I30" t="s">
-        <v>46</v>
-      </c>
-      <c r="K30" s="6"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J30" t="s">
+        <v>46</v>
+      </c>
+      <c r="L30" s="6"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>140</v>
       </c>
@@ -3722,20 +4513,23 @@
         <v>44</v>
       </c>
       <c r="F31" t="s">
+        <v>381</v>
+      </c>
+      <c r="G31" t="s">
         <v>212</v>
       </c>
-      <c r="G31" t="s">
-        <v>22</v>
-      </c>
       <c r="H31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I31" t="s">
-        <v>46</v>
-      </c>
-      <c r="K31" s="6"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J31" t="s">
+        <v>46</v>
+      </c>
+      <c r="L31" s="6"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>141</v>
       </c>
@@ -3752,20 +4546,23 @@
         <v>44</v>
       </c>
       <c r="F32" t="s">
+        <v>399</v>
+      </c>
+      <c r="G32" t="s">
         <v>210</v>
       </c>
-      <c r="G32" t="s">
-        <v>22</v>
-      </c>
       <c r="H32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I32" t="s">
-        <v>46</v>
-      </c>
-      <c r="K32" s="6"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J32" t="s">
+        <v>46</v>
+      </c>
+      <c r="L32" s="6"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>145</v>
       </c>
@@ -3782,20 +4579,23 @@
         <v>44</v>
       </c>
       <c r="F33" t="s">
+        <v>368</v>
+      </c>
+      <c r="G33" t="s">
         <v>78</v>
       </c>
-      <c r="G33" t="s">
-        <v>22</v>
-      </c>
       <c r="H33" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" t="s">
-        <v>46</v>
-      </c>
-      <c r="K33" s="6"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J33" t="s">
+        <v>46</v>
+      </c>
+      <c r="L33" s="6"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>146</v>
       </c>
@@ -3812,19 +4612,22 @@
         <v>44</v>
       </c>
       <c r="F34" t="s">
+        <v>367</v>
+      </c>
+      <c r="G34" t="s">
         <v>78</v>
       </c>
-      <c r="G34" t="s">
-        <v>22</v>
-      </c>
       <c r="H34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I34" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J34" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>150</v>
       </c>
@@ -3841,19 +4644,22 @@
         <v>44</v>
       </c>
       <c r="F35" t="s">
+        <v>419</v>
+      </c>
+      <c r="G35" t="s">
         <v>209</v>
       </c>
-      <c r="G35" t="s">
-        <v>22</v>
-      </c>
       <c r="H35" t="s">
         <v>22</v>
       </c>
       <c r="I35" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J35" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>151</v>
       </c>
@@ -3870,19 +4676,22 @@
         <v>44</v>
       </c>
       <c r="F36" t="s">
+        <v>418</v>
+      </c>
+      <c r="G36" t="s">
         <v>209</v>
       </c>
-      <c r="G36" t="s">
-        <v>22</v>
-      </c>
       <c r="H36" t="s">
         <v>22</v>
       </c>
       <c r="I36" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J36" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>152</v>
       </c>
@@ -3899,19 +4708,22 @@
         <v>44</v>
       </c>
       <c r="F37" t="s">
+        <v>442</v>
+      </c>
+      <c r="G37" t="s">
         <v>209</v>
       </c>
-      <c r="G37" t="s">
-        <v>22</v>
-      </c>
       <c r="H37" t="s">
         <v>22</v>
       </c>
       <c r="I37" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J37" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>153</v>
       </c>
@@ -3928,19 +4740,22 @@
         <v>44</v>
       </c>
       <c r="F38" t="s">
+        <v>450</v>
+      </c>
+      <c r="G38" t="s">
         <v>209</v>
       </c>
-      <c r="G38" t="s">
-        <v>22</v>
-      </c>
       <c r="H38" t="s">
         <v>22</v>
       </c>
       <c r="I38" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J38" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>154</v>
       </c>
@@ -3957,19 +4772,22 @@
         <v>44</v>
       </c>
       <c r="F39" t="s">
+        <v>426</v>
+      </c>
+      <c r="G39" t="s">
         <v>209</v>
       </c>
-      <c r="G39" t="s">
-        <v>22</v>
-      </c>
       <c r="H39" t="s">
         <v>22</v>
       </c>
       <c r="I39" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J39" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>155</v>
       </c>
@@ -3986,19 +4804,22 @@
         <v>44</v>
       </c>
       <c r="F40" t="s">
+        <v>369</v>
+      </c>
+      <c r="G40" t="s">
         <v>209</v>
       </c>
-      <c r="G40" t="s">
-        <v>22</v>
-      </c>
       <c r="H40" t="s">
         <v>22</v>
       </c>
       <c r="I40" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J40" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>156</v>
       </c>
@@ -4015,19 +4836,22 @@
         <v>44</v>
       </c>
       <c r="F41" t="s">
+        <v>421</v>
+      </c>
+      <c r="G41" t="s">
         <v>209</v>
       </c>
-      <c r="G41" t="s">
-        <v>22</v>
-      </c>
       <c r="H41" t="s">
         <v>22</v>
       </c>
       <c r="I41" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J41" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>157</v>
       </c>
@@ -4044,20 +4868,23 @@
         <v>44</v>
       </c>
       <c r="F42" t="s">
+        <v>482</v>
+      </c>
+      <c r="G42" t="s">
         <v>209</v>
       </c>
-      <c r="G42" t="s">
-        <v>22</v>
-      </c>
       <c r="H42" t="s">
         <v>22</v>
       </c>
       <c r="I42" t="s">
-        <v>46</v>
-      </c>
-      <c r="K42" s="6"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J42" t="s">
+        <v>46</v>
+      </c>
+      <c r="L42" s="6"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>158</v>
       </c>
@@ -4074,19 +4901,22 @@
         <v>44</v>
       </c>
       <c r="F43" t="s">
+        <v>443</v>
+      </c>
+      <c r="G43" t="s">
         <v>209</v>
       </c>
-      <c r="G43" t="s">
-        <v>22</v>
-      </c>
       <c r="H43" t="s">
         <v>22</v>
       </c>
       <c r="I43" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J43" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>159</v>
       </c>
@@ -4103,19 +4933,22 @@
         <v>44</v>
       </c>
       <c r="F44" t="s">
+        <v>412</v>
+      </c>
+      <c r="G44" t="s">
         <v>209</v>
       </c>
-      <c r="G44" t="s">
-        <v>22</v>
-      </c>
       <c r="H44" t="s">
         <v>22</v>
       </c>
       <c r="I44" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J44" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>160</v>
       </c>
@@ -4132,19 +4965,22 @@
         <v>44</v>
       </c>
       <c r="F45" t="s">
+        <v>413</v>
+      </c>
+      <c r="G45" t="s">
         <v>209</v>
       </c>
-      <c r="G45" t="s">
-        <v>22</v>
-      </c>
       <c r="H45" t="s">
         <v>22</v>
       </c>
       <c r="I45" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J45" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>161</v>
       </c>
@@ -4161,19 +4997,22 @@
         <v>44</v>
       </c>
       <c r="F46" t="s">
+        <v>439</v>
+      </c>
+      <c r="G46" t="s">
         <v>209</v>
       </c>
-      <c r="G46" t="s">
-        <v>22</v>
-      </c>
       <c r="H46" t="s">
         <v>22</v>
       </c>
       <c r="I46" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>162</v>
       </c>
@@ -4190,19 +5029,22 @@
         <v>44</v>
       </c>
       <c r="F47" t="s">
+        <v>429</v>
+      </c>
+      <c r="G47" t="s">
         <v>209</v>
       </c>
-      <c r="G47" t="s">
-        <v>22</v>
-      </c>
       <c r="H47" t="s">
         <v>22</v>
       </c>
       <c r="I47" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J47" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>163</v>
       </c>
@@ -4219,19 +5061,22 @@
         <v>44</v>
       </c>
       <c r="F48" t="s">
+        <v>430</v>
+      </c>
+      <c r="G48" t="s">
         <v>209</v>
       </c>
-      <c r="G48" t="s">
-        <v>22</v>
-      </c>
       <c r="H48" t="s">
         <v>22</v>
       </c>
       <c r="I48" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J48" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>164</v>
       </c>
@@ -4248,19 +5093,22 @@
         <v>44</v>
       </c>
       <c r="F49" t="s">
+        <v>414</v>
+      </c>
+      <c r="G49" t="s">
         <v>209</v>
       </c>
-      <c r="G49" t="s">
-        <v>22</v>
-      </c>
       <c r="H49" t="s">
         <v>22</v>
       </c>
       <c r="I49" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J49" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>165</v>
       </c>
@@ -4277,19 +5125,22 @@
         <v>44</v>
       </c>
       <c r="F50" t="s">
+        <v>424</v>
+      </c>
+      <c r="G50" t="s">
         <v>209</v>
       </c>
-      <c r="G50" t="s">
-        <v>22</v>
-      </c>
       <c r="H50" t="s">
         <v>22</v>
       </c>
       <c r="I50" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J50" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>170</v>
       </c>
@@ -4306,19 +5157,22 @@
         <v>44</v>
       </c>
       <c r="F51" t="s">
+        <v>459</v>
+      </c>
+      <c r="G51" t="s">
         <v>209</v>
       </c>
-      <c r="G51" t="s">
-        <v>22</v>
-      </c>
       <c r="H51" t="s">
         <v>22</v>
       </c>
       <c r="I51" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J51" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>171</v>
       </c>
@@ -4335,19 +5189,22 @@
         <v>44</v>
       </c>
       <c r="F52" t="s">
+        <v>483</v>
+      </c>
+      <c r="G52" t="s">
         <v>209</v>
       </c>
-      <c r="G52" t="s">
-        <v>22</v>
-      </c>
       <c r="H52" t="s">
         <v>22</v>
       </c>
       <c r="I52" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J52" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>172</v>
       </c>
@@ -4364,19 +5221,22 @@
         <v>44</v>
       </c>
       <c r="F53" t="s">
+        <v>427</v>
+      </c>
+      <c r="G53" t="s">
         <v>209</v>
       </c>
-      <c r="G53" t="s">
-        <v>22</v>
-      </c>
       <c r="H53" t="s">
         <v>22</v>
       </c>
       <c r="I53" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J53" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>173</v>
       </c>
@@ -4393,19 +5253,22 @@
         <v>44</v>
       </c>
       <c r="F54" t="s">
+        <v>441</v>
+      </c>
+      <c r="G54" t="s">
         <v>209</v>
       </c>
-      <c r="G54" t="s">
-        <v>22</v>
-      </c>
       <c r="H54" t="s">
         <v>22</v>
       </c>
       <c r="I54" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J54" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>174</v>
       </c>
@@ -4422,19 +5285,22 @@
         <v>44</v>
       </c>
       <c r="F55" t="s">
+        <v>410</v>
+      </c>
+      <c r="G55" t="s">
         <v>209</v>
       </c>
-      <c r="G55" t="s">
-        <v>22</v>
-      </c>
       <c r="H55" t="s">
         <v>22</v>
       </c>
       <c r="I55" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J55" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>175</v>
       </c>
@@ -4451,19 +5317,22 @@
         <v>44</v>
       </c>
       <c r="F56" t="s">
+        <v>440</v>
+      </c>
+      <c r="G56" t="s">
         <v>209</v>
       </c>
-      <c r="G56" t="s">
-        <v>22</v>
-      </c>
       <c r="H56" t="s">
         <v>22</v>
       </c>
       <c r="I56" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J56" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>176</v>
       </c>
@@ -4480,19 +5349,22 @@
         <v>44</v>
       </c>
       <c r="F57" t="s">
+        <v>409</v>
+      </c>
+      <c r="G57" t="s">
         <v>209</v>
       </c>
-      <c r="G57" t="s">
-        <v>22</v>
-      </c>
       <c r="H57" t="s">
         <v>22</v>
       </c>
       <c r="I57" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J57" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>177</v>
       </c>
@@ -4509,19 +5381,22 @@
         <v>44</v>
       </c>
       <c r="F58" t="s">
+        <v>435</v>
+      </c>
+      <c r="G58" t="s">
         <v>209</v>
       </c>
-      <c r="G58" t="s">
-        <v>22</v>
-      </c>
       <c r="H58" t="s">
         <v>22</v>
       </c>
       <c r="I58" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J58" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>178</v>
       </c>
@@ -4538,19 +5413,22 @@
         <v>44</v>
       </c>
       <c r="F59" t="s">
+        <v>446</v>
+      </c>
+      <c r="G59" t="s">
         <v>209</v>
       </c>
-      <c r="G59" t="s">
-        <v>22</v>
-      </c>
       <c r="H59" t="s">
         <v>22</v>
       </c>
       <c r="I59" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J59" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>184</v>
       </c>
@@ -4567,19 +5445,22 @@
         <v>44</v>
       </c>
       <c r="F60" t="s">
+        <v>400</v>
+      </c>
+      <c r="G60" t="s">
         <v>85</v>
       </c>
-      <c r="G60" t="s">
-        <v>22</v>
-      </c>
       <c r="H60" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I60" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>216</v>
       </c>
@@ -4595,13 +5476,51 @@
       <c r="E61" t="s">
         <v>44</v>
       </c>
+      <c r="F61" t="s">
+        <v>395</v>
+      </c>
       <c r="G61" t="s">
-        <v>22</v>
+        <v>476</v>
       </c>
       <c r="H61" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I61" t="s">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B62" t="s">
+        <v>312</v>
+      </c>
+      <c r="C62" t="s">
+        <v>313</v>
+      </c>
+      <c r="D62" t="s">
+        <v>90</v>
+      </c>
+      <c r="E62" t="s">
+        <v>314</v>
+      </c>
+      <c r="F62" t="s">
+        <v>469</v>
+      </c>
+      <c r="G62" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" t="s">
+        <v>22</v>
+      </c>
+      <c r="I62" t="s">
+        <v>21</v>
+      </c>
+      <c r="J62" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4613,21 +5532,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4D6EF6-B5CA-4DD8-8E99-0F5106178333}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.21875" customWidth="1"/>
     <col min="2" max="2" width="30.77734375" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" customWidth="1"/>
     <col min="4" max="4" width="23.33203125" customWidth="1"/>
-    <col min="5" max="5" width="19.109375" customWidth="1"/>
-    <col min="6" max="6" width="13.109375" customWidth="1"/>
-    <col min="7" max="7" width="18.6640625" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="5" max="6" width="19.109375" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" customWidth="1"/>
+    <col min="8" max="8" width="18.6640625" customWidth="1"/>
+    <col min="9" max="9" width="15.44140625" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>35</v>
       </c>
@@ -4643,20 +5562,21 @@
       <c r="E1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3"/>
+      <c r="G1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>71</v>
       </c>
@@ -4673,20 +5593,23 @@
         <v>44</v>
       </c>
       <c r="F2" t="s">
+        <v>353</v>
+      </c>
+      <c r="G2" t="s">
         <v>85</v>
       </c>
-      <c r="G2" t="s">
-        <v>22</v>
-      </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J2" s="1"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>190</v>
       </c>
@@ -4703,19 +5626,22 @@
         <v>44</v>
       </c>
       <c r="F3" t="s">
+        <v>454</v>
+      </c>
+      <c r="G3" t="s">
         <v>81</v>
       </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>191</v>
       </c>
@@ -4732,19 +5658,22 @@
         <v>44</v>
       </c>
       <c r="F4" t="s">
+        <v>411</v>
+      </c>
+      <c r="G4" t="s">
         <v>81</v>
       </c>
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>192</v>
       </c>
@@ -4761,19 +5690,22 @@
         <v>44</v>
       </c>
       <c r="F5" t="s">
+        <v>460</v>
+      </c>
+      <c r="G5" t="s">
         <v>81</v>
       </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>193</v>
       </c>
@@ -4790,19 +5722,22 @@
         <v>44</v>
       </c>
       <c r="F6" t="s">
+        <v>463</v>
+      </c>
+      <c r="G6" t="s">
         <v>81</v>
       </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>194</v>
       </c>
@@ -4819,19 +5754,22 @@
         <v>44</v>
       </c>
       <c r="F7" t="s">
+        <v>461</v>
+      </c>
+      <c r="G7" t="s">
         <v>81</v>
       </c>
-      <c r="G7" t="s">
-        <v>22</v>
-      </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>195</v>
       </c>
@@ -4848,19 +5786,22 @@
         <v>44</v>
       </c>
       <c r="F8" t="s">
+        <v>415</v>
+      </c>
+      <c r="G8" t="s">
         <v>81</v>
       </c>
-      <c r="G8" t="s">
-        <v>22</v>
-      </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>196</v>
       </c>
@@ -4877,19 +5818,22 @@
         <v>44</v>
       </c>
       <c r="F9" t="s">
+        <v>462</v>
+      </c>
+      <c r="G9" t="s">
         <v>208</v>
       </c>
-      <c r="G9" t="s">
-        <v>21</v>
-      </c>
       <c r="H9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>197</v>
       </c>
@@ -4906,19 +5850,22 @@
         <v>44</v>
       </c>
       <c r="F10" t="s">
+        <v>434</v>
+      </c>
+      <c r="G10" t="s">
         <v>208</v>
       </c>
-      <c r="G10" t="s">
-        <v>21</v>
-      </c>
       <c r="H10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>198</v>
       </c>
@@ -4935,19 +5882,22 @@
         <v>44</v>
       </c>
       <c r="F11" t="s">
+        <v>466</v>
+      </c>
+      <c r="G11" t="s">
         <v>208</v>
       </c>
-      <c r="G11" t="s">
-        <v>21</v>
-      </c>
       <c r="H11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>215</v>
       </c>
@@ -4964,15 +5914,18 @@
         <v>44</v>
       </c>
       <c r="F12" t="s">
+        <v>433</v>
+      </c>
+      <c r="G12" t="s">
         <v>81</v>
       </c>
-      <c r="G12" t="s">
-        <v>22</v>
-      </c>
       <c r="H12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4984,17 +5937,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63C492E2-D2E4-47B8-BA57-BE10C66E0F29}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
     <col min="2" max="2" width="83.5546875" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" customWidth="1"/>
     <col min="4" max="4" width="28.6640625" customWidth="1"/>
-    <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.77734375" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+    <col min="6" max="6" width="17.44140625" customWidth="1"/>
+    <col min="9" max="9" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>35</v>
       </c>
@@ -5010,20 +5966,21 @@
       <c r="E1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3"/>
+      <c r="G1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>199</v>
       </c>
@@ -5040,19 +5997,22 @@
         <v>44</v>
       </c>
       <c r="F2" t="s">
+        <v>407</v>
+      </c>
+      <c r="G2" t="s">
         <v>81</v>
       </c>
-      <c r="G2" t="s">
-        <v>22</v>
-      </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>200</v>
       </c>
@@ -5069,19 +6029,22 @@
         <v>44</v>
       </c>
       <c r="F3" t="s">
+        <v>453</v>
+      </c>
+      <c r="G3" t="s">
         <v>56</v>
       </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>201</v>
       </c>
@@ -5098,19 +6061,22 @@
         <v>44</v>
       </c>
       <c r="F4" t="s">
+        <v>428</v>
+      </c>
+      <c r="G4" t="s">
         <v>56</v>
       </c>
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>202</v>
       </c>
@@ -5127,19 +6093,22 @@
         <v>44</v>
       </c>
       <c r="F5" t="s">
+        <v>465</v>
+      </c>
+      <c r="G5" t="s">
         <v>56</v>
       </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>203</v>
       </c>
@@ -5156,19 +6125,22 @@
         <v>44</v>
       </c>
       <c r="F6" t="s">
+        <v>431</v>
+      </c>
+      <c r="G6" t="s">
         <v>56</v>
       </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>204</v>
       </c>
@@ -5185,19 +6157,22 @@
         <v>44</v>
       </c>
       <c r="F7" t="s">
+        <v>464</v>
+      </c>
+      <c r="G7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" t="s">
-        <v>22</v>
-      </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>205</v>
       </c>
@@ -5214,19 +6189,22 @@
         <v>44</v>
       </c>
       <c r="F8" t="s">
+        <v>425</v>
+      </c>
+      <c r="G8" t="s">
         <v>56</v>
       </c>
-      <c r="G8" t="s">
-        <v>22</v>
-      </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>206</v>
       </c>
@@ -5243,19 +6221,22 @@
         <v>44</v>
       </c>
       <c r="F9" t="s">
+        <v>378</v>
+      </c>
+      <c r="G9" t="s">
         <v>56</v>
       </c>
-      <c r="G9" t="s">
-        <v>22</v>
-      </c>
       <c r="H9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>207</v>
       </c>
@@ -5272,15 +6253,18 @@
         <v>44</v>
       </c>
       <c r="F10" t="s">
+        <v>380</v>
+      </c>
+      <c r="G10" t="s">
         <v>56</v>
       </c>
-      <c r="G10" t="s">
-        <v>22</v>
-      </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5292,23 +6276,23 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{069718ED-836B-4ECE-B422-AFE2CF949AB2}">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="50.77734375" customWidth="1"/>
     <col min="3" max="3" width="8.88671875" customWidth="1"/>
     <col min="4" max="4" width="17.21875" customWidth="1"/>
-    <col min="5" max="5" width="16.21875" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" customWidth="1"/>
-    <col min="8" max="8" width="19.109375" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" customWidth="1"/>
-    <col min="10" max="10" width="19.33203125" customWidth="1"/>
-    <col min="11" max="11" width="28.109375" customWidth="1"/>
-    <col min="12" max="12" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="16.21875" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" customWidth="1"/>
+    <col min="9" max="9" width="19.109375" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" customWidth="1"/>
+    <col min="11" max="11" width="19.33203125" customWidth="1"/>
+    <col min="12" max="12" width="28.109375" customWidth="1"/>
+    <col min="13" max="13" width="23.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>35</v>
       </c>
@@ -5324,21 +6308,22 @@
       <c r="E1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3"/>
+      <c r="G1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="7"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M1" s="7"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -5355,19 +6340,22 @@
         <v>44</v>
       </c>
       <c r="F2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G2" t="s">
         <v>47</v>
       </c>
-      <c r="G2" t="s">
-        <v>22</v>
-      </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -5384,19 +6372,22 @@
         <v>44</v>
       </c>
       <c r="F3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G3" t="s">
         <v>50</v>
       </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -5413,19 +6404,22 @@
         <v>45</v>
       </c>
       <c r="F4" t="s">
+        <v>325</v>
+      </c>
+      <c r="G4" t="s">
         <v>49</v>
       </c>
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -5442,19 +6436,22 @@
         <v>45</v>
       </c>
       <c r="F5" t="s">
+        <v>360</v>
+      </c>
+      <c r="G5" t="s">
         <v>48</v>
       </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>58</v>
       </c>
@@ -5471,19 +6468,22 @@
         <v>44</v>
       </c>
       <c r="F6" t="s">
+        <v>473</v>
+      </c>
+      <c r="G6" t="s">
         <v>65</v>
       </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>62</v>
       </c>
@@ -5500,19 +6500,22 @@
         <v>44</v>
       </c>
       <c r="F7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G7" t="s">
         <v>66</v>
       </c>
-      <c r="G7" t="s">
-        <v>22</v>
-      </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>67</v>
       </c>
@@ -5529,19 +6532,22 @@
         <v>44</v>
       </c>
       <c r="F8" t="s">
+        <v>330</v>
+      </c>
+      <c r="G8" t="s">
         <v>78</v>
       </c>
-      <c r="G8" t="s">
-        <v>22</v>
-      </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>69</v>
       </c>
@@ -5558,19 +6564,22 @@
         <v>45</v>
       </c>
       <c r="F9" t="s">
+        <v>393</v>
+      </c>
+      <c r="G9" t="s">
         <v>84</v>
       </c>
-      <c r="G9" t="s">
-        <v>22</v>
-      </c>
       <c r="H9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>77</v>
       </c>
@@ -5587,19 +6596,22 @@
         <v>44</v>
       </c>
       <c r="F10" t="s">
+        <v>379</v>
+      </c>
+      <c r="G10" t="s">
         <v>79</v>
       </c>
-      <c r="G10" t="s">
-        <v>22</v>
-      </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>83</v>
       </c>
@@ -5616,19 +6628,22 @@
         <v>44</v>
       </c>
       <c r="F11" t="s">
+        <v>343</v>
+      </c>
+      <c r="G11" t="s">
         <v>64</v>
       </c>
-      <c r="G11" t="s">
-        <v>22</v>
-      </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>91</v>
       </c>
@@ -5644,17 +6659,23 @@
       <c r="E12" t="s">
         <v>45</v>
       </c>
+      <c r="F12" t="s">
+        <v>402</v>
+      </c>
       <c r="G12" t="s">
-        <v>22</v>
+        <v>481</v>
       </c>
       <c r="H12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>98</v>
       </c>
@@ -5671,19 +6692,22 @@
         <v>45</v>
       </c>
       <c r="F13" t="s">
+        <v>345</v>
+      </c>
+      <c r="G13" t="s">
         <v>209</v>
       </c>
-      <c r="G13" t="s">
-        <v>22</v>
-      </c>
       <c r="H13" t="s">
         <v>22</v>
       </c>
       <c r="I13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="J13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>99</v>
       </c>
@@ -5700,19 +6724,22 @@
         <v>44</v>
       </c>
       <c r="F14" t="s">
+        <v>341</v>
+      </c>
+      <c r="G14" t="s">
         <v>81</v>
       </c>
-      <c r="G14" t="s">
-        <v>22</v>
-      </c>
       <c r="H14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I14" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>112</v>
       </c>
@@ -5729,19 +6756,22 @@
         <v>44</v>
       </c>
       <c r="F15" t="s">
+        <v>403</v>
+      </c>
+      <c r="G15" t="s">
         <v>213</v>
       </c>
-      <c r="G15" t="s">
-        <v>22</v>
-      </c>
       <c r="H15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>114</v>
       </c>
@@ -5758,19 +6788,22 @@
         <v>44</v>
       </c>
       <c r="F16" t="s">
+        <v>372</v>
+      </c>
+      <c r="G16" t="s">
         <v>209</v>
       </c>
-      <c r="G16" t="s">
-        <v>22</v>
-      </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>126</v>
       </c>
@@ -5787,19 +6820,22 @@
         <v>44</v>
       </c>
       <c r="F17" t="s">
+        <v>386</v>
+      </c>
+      <c r="G17" t="s">
         <v>64</v>
       </c>
-      <c r="G17" t="s">
-        <v>22</v>
-      </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>127</v>
       </c>
@@ -5816,20 +6852,23 @@
         <v>44</v>
       </c>
       <c r="F18" t="s">
+        <v>385</v>
+      </c>
+      <c r="G18" t="s">
         <v>209</v>
       </c>
-      <c r="G18" t="s">
-        <v>22</v>
-      </c>
       <c r="H18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I18" t="s">
-        <v>46</v>
-      </c>
-      <c r="K18" s="6"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J18" t="s">
+        <v>46</v>
+      </c>
+      <c r="L18" s="6"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>129</v>
       </c>
@@ -5846,20 +6885,23 @@
         <v>44</v>
       </c>
       <c r="F19" t="s">
+        <v>363</v>
+      </c>
+      <c r="G19" t="s">
         <v>214</v>
       </c>
-      <c r="G19" t="s">
-        <v>22</v>
-      </c>
       <c r="H19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I19" t="s">
-        <v>46</v>
-      </c>
-      <c r="K19" s="6"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J19" t="s">
+        <v>46</v>
+      </c>
+      <c r="L19" s="6"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>142</v>
       </c>
@@ -5876,20 +6918,23 @@
         <v>44</v>
       </c>
       <c r="F20" t="s">
+        <v>390</v>
+      </c>
+      <c r="G20" t="s">
         <v>84</v>
       </c>
-      <c r="G20" t="s">
-        <v>22</v>
-      </c>
       <c r="H20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I20" t="s">
-        <v>46</v>
-      </c>
-      <c r="K20" s="6"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J20" t="s">
+        <v>46</v>
+      </c>
+      <c r="L20" s="6"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>167</v>
       </c>
@@ -5906,19 +6951,22 @@
         <v>45</v>
       </c>
       <c r="F21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G21" t="s">
         <v>78</v>
       </c>
-      <c r="G21" t="s">
-        <v>22</v>
-      </c>
       <c r="H21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>182</v>
       </c>
@@ -5935,19 +6983,22 @@
         <v>44</v>
       </c>
       <c r="F22" t="s">
+        <v>416</v>
+      </c>
+      <c r="G22" t="s">
         <v>213</v>
       </c>
-      <c r="G22" t="s">
-        <v>22</v>
-      </c>
       <c r="H22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I22" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>188</v>
       </c>
@@ -5964,19 +7015,22 @@
         <v>44</v>
       </c>
       <c r="F23" t="s">
+        <v>447</v>
+      </c>
+      <c r="G23" t="s">
         <v>81</v>
       </c>
-      <c r="G23" t="s">
-        <v>22</v>
-      </c>
       <c r="H23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I23" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>220</v>
       </c>
@@ -5992,14 +7046,43 @@
       <c r="E24" t="s">
         <v>45</v>
       </c>
+      <c r="F24" t="s">
+        <v>396</v>
+      </c>
       <c r="G24" t="s">
-        <v>22</v>
+        <v>322</v>
       </c>
       <c r="H24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I24" t="s">
-        <v>46</v>
+        <v>21</v>
+      </c>
+      <c r="J24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>309</v>
+      </c>
+      <c r="B25" t="s">
+        <v>310</v>
+      </c>
+      <c r="C25" t="s">
+        <v>245</v>
+      </c>
+      <c r="D25" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" t="s">
+        <v>44</v>
+      </c>
+      <c r="F25" t="s">
+        <v>474</v>
+      </c>
+      <c r="G25" t="s">
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -6010,20 +7093,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72021BD4-A7C6-41F2-A539-ED5728AA43D0}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="26.5546875" customWidth="1"/>
     <col min="4" max="4" width="17.44140625" customWidth="1"/>
-    <col min="5" max="5" width="18.5546875" customWidth="1"/>
-    <col min="6" max="6" width="13.77734375" customWidth="1"/>
-    <col min="7" max="7" width="20.33203125" customWidth="1"/>
-    <col min="8" max="8" width="19.109375" customWidth="1"/>
-    <col min="10" max="10" width="20.5546875" customWidth="1"/>
+    <col min="5" max="6" width="18.5546875" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" customWidth="1"/>
+    <col min="9" max="9" width="19.109375" customWidth="1"/>
+    <col min="11" max="11" width="20.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>35</v>
       </c>
@@ -6039,20 +7122,21 @@
       <c r="E1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3"/>
+      <c r="G1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>82</v>
       </c>
@@ -6069,19 +7153,22 @@
         <v>44</v>
       </c>
       <c r="F2" t="s">
+        <v>472</v>
+      </c>
+      <c r="G2" t="s">
         <v>81</v>
       </c>
-      <c r="G2" t="s">
-        <v>22</v>
-      </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>96</v>
       </c>
@@ -6098,19 +7185,22 @@
         <v>45</v>
       </c>
       <c r="F3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G3" t="s">
         <v>211</v>
       </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>130</v>
       </c>
@@ -6127,15 +7217,18 @@
         <v>44</v>
       </c>
       <c r="F4" t="s">
+        <v>444</v>
+      </c>
+      <c r="G4" t="s">
         <v>211</v>
       </c>
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
         <v>46</v>
       </c>
     </row>
